--- a/Experiences/Mesures brutes colle.xlsx
+++ b/Experiences/Mesures brutes colle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Mines IC\TR Fluide\VS\Experiences\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A903B2-C96B-47C1-81D7-6FA561130A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549FF945-2177-4999-9C6D-75CF0BA7704C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9360" yWindow="330" windowWidth="9680" windowHeight="9490" xr2:uid="{9AB0AB11-A7EF-40E7-B41F-31F80C89CE16}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9AB0AB11-A7EF-40E7-B41F-31F80C89CE16}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -450,7 +450,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B2" s="1">
         <v>4.1804000000000001E-2</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B3" s="1">
         <v>4.1804000000000001E-2</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B4" s="1">
         <v>4.1804000000000001E-2</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B5" s="1">
         <v>4.1804000000000001E-2</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B6" s="1">
         <v>4.1804000000000001E-2</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B7" s="1">
         <v>0.10015300000000001</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B8" s="1">
         <v>0.10015300000000001</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B9" s="1">
         <v>0.10015300000000001</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B10" s="1">
         <v>0.10015300000000001</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B11" s="1">
         <v>2.001E-2</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B12" s="1">
         <v>2.001E-2</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B13" s="1">
         <v>2.001E-2</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B14" s="1">
         <v>0.100025</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B15" s="1">
         <v>0.100025</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B16" s="1">
         <v>0.100025</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B17" s="1">
         <v>0.100025</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B18" s="1">
         <v>4.1804000000000001E-2</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B19" s="1">
         <v>4.1804000000000001E-2</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B20" s="1">
         <v>2.001E-2</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B21" s="1">
         <v>2.001E-2</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B22" s="1">
         <v>2.001E-2</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B23" s="1">
         <v>0.20005999999999999</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B24" s="1">
         <v>0.20005999999999999</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
-        <v>5.5000000000000003E-4</v>
+        <v>5.5000000000000002E-5</v>
       </c>
       <c r="B25" s="1">
         <v>0.20005999999999999</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B26" s="1">
         <v>0.20005999999999999</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B27" s="1">
         <v>0.20005999999999999</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
-        <v>9.5E-4</v>
+        <v>9.5000000000000005E-5</v>
       </c>
       <c r="B28" s="1">
         <v>0.20005999999999999</v>
@@ -1313,68 +1313,24 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
-        <v>5.5000000000000003E-4</v>
-      </c>
-      <c r="B29" s="1">
-        <v>310</v>
-      </c>
-      <c r="C29">
-        <v>12.44</v>
-      </c>
-      <c r="D29">
-        <v>25.3</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1270</v>
-      </c>
-      <c r="F29" s="1">
-        <v>15</v>
-      </c>
-      <c r="G29" s="1">
-        <v>90</v>
-      </c>
-      <c r="H29" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I29" s="1">
-        <v>907</v>
-      </c>
-      <c r="J29" s="1">
-        <v>9.81</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
-        <v>5.5000000000000003E-4</v>
-      </c>
-      <c r="B30" s="1">
-        <v>260</v>
-      </c>
-      <c r="C30">
-        <v>8.75</v>
-      </c>
-      <c r="D30">
-        <v>22.15</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1270</v>
-      </c>
-      <c r="F30" s="1">
-        <v>15</v>
-      </c>
-      <c r="G30" s="1">
-        <v>90</v>
-      </c>
-      <c r="H30" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="I30" s="1">
-        <v>907</v>
-      </c>
-      <c r="J30" s="1">
-        <v>9.81</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
